--- a/data/result/validation_errors.xlsx
+++ b/data/result/validation_errors.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,36 +413,36 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Row_Number</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Column_Name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Invalid_Value</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Error_Type</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
         <is>
           <t>Severity</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Column_Name</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Invalid_Value</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Error_Type</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Error_Message</t>
         </is>
@@ -462,273 +450,469 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>41</v>
-      </c>
-      <c r="B2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>invoice_number</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>inv-0</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>COMPOSITE_DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>invoice_number</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>INV-UNIQUE-1</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>VALIDATION_FAILED</t>
-        </is>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Composite duplicate: ('inv-unique-1', 'cust-555')</t>
+          <t>Original row flagged: Conflict with row 3</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>202</v>
-      </c>
-      <c r="B3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>invoice_number</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>INV-0</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>COMPOSITE_DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>invoice_number</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>INV-1002</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>VALIDATION_FAILED</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Composite duplicate: ('inv-1002', 'cust-202')</t>
+          <t>Duplicate of row 2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>10</v>
-      </c>
-      <c r="B4" t="n">
+        <v>31</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>CompanyCompanyCompanyCompanyCompanyCompanyCompanyCompanyCompanyCompanyCompanyCompanyCompanyCompanyCompanyCompanyCompanyCompany 28</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>BUSINESS_RULE_VIOLATION</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
         <v>2</v>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>sd</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>VALIDATION_FAILED</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Value not in allowed list: ['active', 'pending', 'closed', 'suspend']</t>
+          <t>Too long (Max: 50)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>32</v>
-      </c>
-      <c r="B5" t="n">
-        <v>2</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>amount</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>VALIDATION_FAILED</t>
-        </is>
+        <v>103</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>customer_code</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>MISSING_REQUIRED</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Field 'amount' is required.</t>
+          <t>Mandatory field is empty</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>33</v>
-      </c>
-      <c r="B6" t="n">
-        <v>2</v>
+        <v>203</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>project_code</t>
+        </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>amount</t>
+          <t>WRONG-CODE</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>TEN_DOLLARS</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>VALIDATION_FAILED</t>
-        </is>
+          <t>PATTERN_MISMATCH</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>3</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>could not convert string to float: 'TEN_DOLLARS'</t>
+          <t>Invalid pattern: WRONG-CODE</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>35</v>
-      </c>
-      <c r="B7" t="n">
+        <v>303</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>BUSINESS_RULE_VIOLATION</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
         <v>2</v>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Ab</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>VALIDATION_FAILED</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Length less than 3</t>
+          <t>Constraint: Since status is suspend, this must be None</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>36</v>
-      </c>
-      <c r="B8" t="n">
-        <v>2</v>
+        <v>403</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>customer_code</t>
+        </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>amount</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>500.5</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>VALIDATION_FAILED</t>
-        </is>
+          <t>CUST-X</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>PATTERN_MISMATCH</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Amount must be 0 when status is suspend</t>
+          <t>Invalid pattern: CUST-X</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>34</v>
-      </c>
-      <c r="B9" t="n">
-        <v>3</v>
+        <v>404</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>customer_code</t>
+        </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>project_code</t>
+          <t>CUST-X</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>WRONG-FORMAT</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>VALIDATION_FAILED</t>
-        </is>
+          <t>PATTERN_MISMATCH</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Pattern mismatch</t>
+          <t>Invalid pattern: CUST-X</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>38</v>
-      </c>
-      <c r="B10" t="n">
-        <v>3</v>
+        <v>94</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>invoice_number</t>
+        </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>inv-91</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2027-01-01</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>VALIDATION_FAILED</t>
-        </is>
+          <t>COMPOSITE_DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Year later than 2026</t>
+          <t>Original row flagged: Conflict with row 448</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>39</v>
-      </c>
-      <c r="B11" t="n">
-        <v>3</v>
+        <v>448</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>invoice_number</t>
+        </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>created_at</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>4654654.23</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>VALIDATION_FAILED</t>
-        </is>
+          <t>INV-91</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>COMPOSITE_DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Datetime processing failed: cannot convert input with unit 'D'</t>
+          <t>Duplicate of row 94</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>504</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>customer_code</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CUST-Y</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>PATTERN_MISMATCH</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Invalid pattern: CUST-Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>505</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>customer_code</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CUST-Y</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>PATTERN_MISMATCH</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Invalid pattern: CUST-Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>506</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>customer_code</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CUST-Y</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>PATTERN_MISMATCH</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Invalid pattern: CUST-Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>704</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>invalid_email.com</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>PATTERN_MISMATCH</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>2</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Invalid email format: 'invalid_email.com'</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>804</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>TEXT_DATA</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>TYPE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Expected float but got: 'TEXT_DATA'</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>75004</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>df</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>TYPE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>2</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Expected float but got: 'df'</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>75005</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>MISSING_REQUIRED</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>2</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Mandatory field is empty</t>
         </is>
       </c>
     </row>

--- a/data/result/validation_errors.xlsx
+++ b/data/result/validation_errors.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -506,21 +506,17 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>CompanyCompanyCompanyCompanyCompanyCompanyCompanyCompanyCompanyCompanyCompanyCompanyCompanyCompanyCompanyCompanyCompanyCompany 28</t>
-        </is>
-      </c>
+          <t>branch</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>BUSINESS_RULE_VIOLATION</t>
+          <t>MISSING_REQUIRED</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -528,121 +524,121 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Too long (Max: 50)</t>
+          <t>Mandatory field is empty</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>103</v>
+        <v>31</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>customer_code</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>CompanyCompanyCompanyCompanyCompanyCompanyCompanyCompanyCompanyCompanyCompanyCompanyCompanyCompanyCompanyCompanyCompanyCompany 28</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>MISSING_REQUIRED</t>
+          <t>BUSINESS_RULE_VIOLATION</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mandatory field is empty</t>
+          <t>Too long (Max: 50)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>203</v>
+        <v>103</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>project_code</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>WRONG-CODE</t>
-        </is>
-      </c>
+          <t>customer_code</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>PATTERN_MISMATCH</t>
+          <t>MISSING_REQUIRED</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Invalid pattern: WRONG-CODE</t>
+          <t>Mandatory field is empty</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>303</v>
+        <v>203</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>amount</t>
+          <t>project_code</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>WRONG-CODE</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>BUSINESS_RULE_VIOLATION</t>
+          <t>PATTERN_MISMATCH</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Constraint: Since status is suspend, this must be None</t>
+          <t>Invalid pattern: WRONG-CODE</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>403</v>
+        <v>303</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>customer_code</t>
+          <t>amount</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CUST-X</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>PATTERN_MISMATCH</t>
+          <t>BUSINESS_RULE_VIOLATION</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Invalid pattern: CUST-X</t>
+          <t>Constraint: Since status is suspend, this must be None</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -670,21 +666,21 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>94</v>
+        <v>404</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>invoice_number</t>
+          <t>customer_code</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>inv-91</t>
+          <t>CUST-X</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>COMPOSITE_DUPLICATE</t>
+          <t>PATTERN_MISMATCH</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -692,13 +688,13 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Original row flagged: Conflict with row 448</t>
+          <t>Invalid pattern: CUST-X</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>448</v>
+        <v>94</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -707,7 +703,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>INV-91</t>
+          <t>inv-91</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -720,27 +716,27 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Duplicate of row 94</t>
+          <t>Original row flagged: Conflict with row 448</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>504</v>
+        <v>448</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>customer_code</t>
+          <t>invoice_number</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CUST-Y</t>
+          <t>INV-91</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>PATTERN_MISMATCH</t>
+          <t>COMPOSITE_DUPLICATE</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -748,13 +744,13 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Invalid pattern: CUST-Y</t>
+          <t>Duplicate of row 94</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -782,7 +778,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -810,16 +806,16 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>704</v>
+        <v>506</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>customer_code</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>invalid_email.com</t>
+          <t>CUST-Y</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -828,31 +824,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Invalid email format: 'invalid_email.com'</t>
+          <t>Invalid pattern: CUST-Y</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>804</v>
+        <v>704</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>amount</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>TEXT_DATA</t>
+          <t>invalid_email.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>TYPE_MISMATCH</t>
+          <t>PATTERN_MISMATCH</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -860,13 +856,13 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Expected float but got: 'TEXT_DATA'</t>
+          <t>Invalid email format: 'invalid_email.com'</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>75004</v>
+        <v>804</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -875,7 +871,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>df</t>
+          <t>TEXT_DATA</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -888,29 +884,141 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Expected float but got: 'df'</t>
+          <t>Expected float but got: 'TEXT_DATA'</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>75005</v>
+        <v>60753</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>amount</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
+          <t>branch</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>kj</t>
+        </is>
+      </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>MISSING_REQUIRED</t>
+          <t>TYPE_MISMATCH</t>
         </is>
       </c>
       <c r="E18" t="n">
         <v>2</v>
       </c>
       <c r="F18" t="inlineStr">
+        <is>
+          <t>Expected float but got: 'kj'</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>74904</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>1/91/2024</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>INVALID_DATE</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>3</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Value '1/91/2024' is not a valid date. Please use YYYY-MM-DD or DD/MM/YYYY.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>74955</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>branch</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>ff</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>TYPE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>2</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Expected float but got: 'ff'</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>75004</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>df</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>TYPE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>2</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Expected float but got: 'df'</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>75005</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>MISSING_REQUIRED</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>2</v>
+      </c>
+      <c r="F22" t="inlineStr">
         <is>
           <t>Mandatory field is empty</t>
         </is>

--- a/data/result/validation_errors.xlsx
+++ b/data/result/validation_errors.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -520,7 +520,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -918,21 +918,21 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>74904</v>
+        <v>60758</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>branch</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1/91/2024</t>
+          <t>5656565</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>INVALID_DATE</t>
+          <t>BUSINESS_RULE_VIOLATION</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -940,87 +940,303 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Value '1/91/2024' is not a valid date. Please use YYYY-MM-DD or DD/MM/YYYY.</t>
+          <t>Value 5656565 must be between 1 and 2999 for branch</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>74955</v>
+        <v>74904</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>branch</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ff</t>
+          <t>1/91/2024</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>TYPE_MISMATCH</t>
+          <t>INVALID_DATE</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Expected float but got: 'ff'</t>
+          <t>Value '1/91/2024' is not a valid date. Please use YYYY-MM-DD or DD/MM/YYYY.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>75004</v>
+        <v>74905</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>amount</t>
+          <t>branch</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>df</t>
+          <t>545454</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>TYPE_MISMATCH</t>
+          <t>BUSINESS_RULE_VIOLATION</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Expected float but got: 'df'</t>
+          <t>Value 545454 must be between 1 and 2999 for branch</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
+        <v>74955</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>branch</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>ff</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>TYPE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>3</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Expected float but got: 'ff'</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>74966</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>branch</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>5251502525</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>BUSINESS_RULE_VIOLATION</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>3</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Value 5251502525 must be between 1 and 2999 for branch</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>75004</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>df</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>TYPE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>2</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Expected float but got: 'df'</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
         <v>75005</v>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr">
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
         <is>
           <t>MISSING_REQUIRED</t>
         </is>
       </c>
-      <c r="E22" t="n">
+      <c r="E25" t="n">
         <v>2</v>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>Mandatory field is empty</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>435</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>invoice_number</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>inv-432</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>COMPOSITE_DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Original row flagged: Conflict with row 75006</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>75006</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>invoice_number</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>INV-432</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>COMPOSITE_DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Duplicate of row 435</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>75007</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>MISSING_REQUIRED</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>2</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Mandatory field is empty</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>75008</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>MISSING_REQUIRED</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>2</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Mandatory field is empty</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>75008</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>سی</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>TYPE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>2</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Expected float but got: 'سی'</t>
         </is>
       </c>
     </row>
